--- a/ingress-workflow_examples/animal/Dejana/OpenField/result/rectangle.xlsx
+++ b/ingress-workflow_examples/animal/Dejana/OpenField/result/rectangle.xlsx
@@ -79,6 +79,30 @@
     <t>Enclosure</t>
   </si>
   <si>
+    <t>721_0</t>
+  </si>
+  <si>
+    <t>722_0</t>
+  </si>
+  <si>
+    <t>723_0</t>
+  </si>
+  <si>
+    <t>781_0</t>
+  </si>
+  <si>
+    <t>782_0</t>
+  </si>
+  <si>
+    <t>845_0</t>
+  </si>
+  <si>
+    <t>846_0</t>
+  </si>
+  <si>
+    <t>847_0</t>
+  </si>
+  <si>
     <t>19103_0</t>
   </si>
   <si>
@@ -92,30 +116,6 @@
   </si>
   <si>
     <t>19205_0</t>
-  </si>
-  <si>
-    <t>721_0</t>
-  </si>
-  <si>
-    <t>722_0</t>
-  </si>
-  <si>
-    <t>723_0</t>
-  </si>
-  <si>
-    <t>781_0</t>
-  </si>
-  <si>
-    <t>782_0</t>
-  </si>
-  <si>
-    <t>845_0</t>
-  </si>
-  <si>
-    <t>846_0</t>
-  </si>
-  <si>
-    <t>847_0</t>
   </si>
 </sst>
 </file>
@@ -695,136 +695,136 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <v>2.475207348613723</v>
+        <v>9.967078811696638</v>
       </c>
       <c r="C4">
-        <v>0.06073134950766249</v>
+        <v>0.05269988680604668</v>
       </c>
       <c r="D4">
-        <v>0.0441855001265534</v>
+        <v>0.02786859256058276</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>72.83333333333333</v>
+        <v>195.5666666666667</v>
       </c>
       <c r="H4">
-        <v>31.37931942599485</v>
+        <v>25.50217949258012</v>
       </c>
       <c r="I4">
-        <v>0.04268891333249619</v>
+        <v>0.05580849123704005</v>
       </c>
       <c r="J4">
-        <v>0.01884064579783603</v>
+        <v>0.02389262304708449</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M4">
-        <v>531.8</v>
+        <v>407.6666666666667</v>
       </c>
       <c r="N4">
-        <v>5.009313241949034</v>
+        <v>10.55177180827448</v>
       </c>
       <c r="O4">
-        <v>0.04844352092900348</v>
+        <v>0.05583918842871605</v>
       </c>
       <c r="P4">
-        <v>0.02485825081661053</v>
+        <v>0.02059383101204121</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S4">
-        <v>88.09999999999999</v>
+        <v>174.4333333333333</v>
       </c>
       <c r="T4">
-        <v>10.02826466477502</v>
+        <v>4.924444728543831</v>
       </c>
       <c r="U4">
-        <v>0.04314394727699146</v>
+        <v>0.06754480530021001</v>
       </c>
       <c r="V4">
-        <v>0.02290550909774942</v>
+        <v>0.03483675311313916</v>
       </c>
       <c r="W4">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y4">
-        <v>164.4666666666667</v>
+        <v>96.86666666666666</v>
       </c>
       <c r="Z4">
-        <v>9.16563475371073</v>
+        <v>8.704515192808024</v>
       </c>
       <c r="AA4">
-        <v>0.03179667060647052</v>
+        <v>0.04438760535717898</v>
       </c>
       <c r="AB4">
-        <v>0.008690025901751421</v>
+        <v>0.01566319201113463</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE4">
-        <v>230.7666666666667</v>
+        <v>179.2</v>
       </c>
       <c r="AF4">
-        <v>7.221757570081047</v>
+        <v>8.650351230052216</v>
       </c>
       <c r="AG4">
-        <v>0.053135260133278</v>
+        <v>0.0550867297795552</v>
       </c>
       <c r="AH4">
-        <v>0.02348830055591478</v>
+        <v>0.02511294664490925</v>
       </c>
       <c r="AI4">
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AK4">
-        <v>121.0333333333333</v>
+        <v>152.7333333333333</v>
       </c>
       <c r="AL4">
-        <v>40.68086661693295</v>
+        <v>40.12689377405692</v>
       </c>
       <c r="AM4">
-        <v>0.03841498564660895</v>
+        <v>0.05505540391091898</v>
       </c>
       <c r="AN4">
-        <v>0.01645345222167316</v>
+        <v>0.02135989808545413</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>18303</v>
+        <v>18166</v>
       </c>
       <c r="AQ4">
-        <v>18139</v>
+        <v>18097</v>
       </c>
       <c r="AR4">
-        <v>610.0609920000001</v>
+        <v>605.56576</v>
       </c>
       <c r="AS4">
-        <v>19103</v>
+        <v>721</v>
       </c>
       <c r="AT4">
         <v>0</v>
@@ -844,136 +844,136 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>8.529108285110652</v>
+        <v>1.815873594863792</v>
       </c>
       <c r="C5">
-        <v>0.04499078238520188</v>
+        <v>0.08304819218565415</v>
       </c>
       <c r="D5">
-        <v>0.02162933790991398</v>
+        <v>0.03741651587611737</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="G5">
-        <v>195.3666666666667</v>
+        <v>117.6666666666667</v>
       </c>
       <c r="H5">
-        <v>22.99860780657122</v>
+        <v>34.04024582189511</v>
       </c>
       <c r="I5">
-        <v>0.04087045881667449</v>
+        <v>0.0580544001432908</v>
       </c>
       <c r="J5">
-        <v>0.01655545333521039</v>
+        <v>0.02970034626768647</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="M5">
-        <v>409.2</v>
+        <v>487.5333333333334</v>
       </c>
       <c r="N5">
-        <v>8.637997750479212</v>
+        <v>11.79612608825212</v>
       </c>
       <c r="O5">
-        <v>0.03860144601924147</v>
+        <v>0.06217011652791928</v>
       </c>
       <c r="P5">
-        <v>0.01772650013879054</v>
+        <v>0.04848282808515434</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="S5">
-        <v>178.6666666666667</v>
+        <v>173.0666666666667</v>
       </c>
       <c r="T5">
-        <v>4.22244599965103</v>
+        <v>5.109931131844242</v>
       </c>
       <c r="U5">
-        <v>0.04199842867477664</v>
+        <v>0.05589688343237483</v>
       </c>
       <c r="V5">
-        <v>0.02258427860908982</v>
+        <v>0.02451647953883943</v>
       </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y5">
-        <v>80.76666666666667</v>
+        <v>100.4666666666667</v>
       </c>
       <c r="Z5">
-        <v>7.069308597250315</v>
+        <v>8.902970291748323</v>
       </c>
       <c r="AA5">
-        <v>0.04059648095619925</v>
+        <v>0.05570094934101161</v>
       </c>
       <c r="AB5">
-        <v>0.01955621171415866</v>
+        <v>0.02662049407872092</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AE5">
-        <v>164.5333333333333</v>
+        <v>178.5</v>
       </c>
       <c r="AF5">
-        <v>9.355762892801522</v>
+        <v>7.547273303133704</v>
       </c>
       <c r="AG5">
-        <v>0.04561874991485529</v>
+        <v>0.05701196494875984</v>
       </c>
       <c r="AH5">
-        <v>0.01774198005817886</v>
+        <v>0.02602330750507253</v>
       </c>
       <c r="AI5">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="AK5">
-        <v>180.6</v>
+        <v>153.1666666666667</v>
       </c>
       <c r="AL5">
-        <v>37.11293807907974</v>
+        <v>53.8401808283724</v>
       </c>
       <c r="AM5">
-        <v>0.04335754850974827</v>
+        <v>0.06788835225418427</v>
       </c>
       <c r="AN5">
-        <v>0.01572001518479627</v>
+        <v>0.02888608338830567</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>18213</v>
+        <v>18210</v>
       </c>
       <c r="AQ5">
-        <v>18137</v>
+        <v>18156</v>
       </c>
       <c r="AR5">
-        <v>607.0718460000001</v>
+        <v>607.03296</v>
       </c>
       <c r="AS5">
-        <v>19105</v>
+        <v>722</v>
       </c>
       <c r="AT5">
         <v>0</v>
@@ -993,136 +993,136 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>4.237605001304678</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.04530467223953804</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.01569935760969847</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>17.13333333333333</v>
+        <v>104.3</v>
       </c>
       <c r="H6">
-        <v>61.36661304449379</v>
+        <v>31.96566926850759</v>
       </c>
       <c r="I6">
-        <v>0.0772284241225088</v>
+        <v>0.05960624207499344</v>
       </c>
       <c r="J6">
-        <v>0.03487259588861157</v>
+        <v>0.02395520346964497</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M6">
-        <v>592.9333333333333</v>
+        <v>498.2</v>
       </c>
       <c r="N6">
-        <v>8.23321849077886</v>
+        <v>10.55914327062204</v>
       </c>
       <c r="O6">
-        <v>0.05188950656047024</v>
+        <v>0.05585320311289647</v>
       </c>
       <c r="P6">
-        <v>0.01646072944499695</v>
+        <v>0.02945370675351297</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S6">
-        <v>162.0333333333333</v>
+        <v>172.1333333333333</v>
       </c>
       <c r="T6">
-        <v>13.70462657525741</v>
+        <v>6.812928094808438</v>
       </c>
       <c r="U6">
-        <v>0.04933389713444322</v>
+        <v>0.06257830791589941</v>
       </c>
       <c r="V6">
-        <v>0.01900499938488739</v>
+        <v>0.01897097032611485</v>
       </c>
       <c r="W6">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="Y6">
-        <v>213.1666666666667</v>
+        <v>114.7333333333333</v>
       </c>
       <c r="Z6">
-        <v>7.1786896163597</v>
+        <v>7.997360326713502</v>
       </c>
       <c r="AA6">
-        <v>0.09681998555195273</v>
+        <v>0.04725837978965134</v>
       </c>
       <c r="AB6">
-        <v>0.05348819887493187</v>
+        <v>0.01565677262707049</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6">
-        <v>93.16666666666667</v>
+        <v>170.3</v>
       </c>
       <c r="AF6">
-        <v>9.186512332141026</v>
+        <v>7.112654001515814</v>
       </c>
       <c r="AG6">
-        <v>0.07881300554622368</v>
+        <v>0.06187038130309771</v>
       </c>
       <c r="AH6">
-        <v>0.0381612515221492</v>
+        <v>0.02370156451450561</v>
       </c>
       <c r="AI6">
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AK6">
-        <v>141.7</v>
+        <v>145.3333333333333</v>
       </c>
       <c r="AL6">
-        <v>69.06773645345442</v>
+        <v>41.40039739795708</v>
       </c>
       <c r="AM6">
-        <v>0.07918891738173295</v>
+        <v>0.05731546322738235</v>
       </c>
       <c r="AN6">
-        <v>0.03182606546806323</v>
+        <v>0.02196282041071163</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>18439</v>
+        <v>18165</v>
       </c>
       <c r="AQ6">
-        <v>18302</v>
+        <v>18075</v>
       </c>
       <c r="AR6">
-        <v>614.663155</v>
+        <v>605.530919</v>
       </c>
       <c r="AS6">
-        <v>19202</v>
+        <v>723</v>
       </c>
       <c r="AT6">
         <v>0</v>
@@ -1142,136 +1142,136 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>1.583241249931628</v>
+        <v>3.506871442636478</v>
       </c>
       <c r="C7">
-        <v>0.03111329839395981</v>
+        <v>0.05037705856498678</v>
       </c>
       <c r="D7">
-        <v>0.01027514518398275</v>
+        <v>0.05316649527279308</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>63.2</v>
+        <v>107.6</v>
       </c>
       <c r="H7">
-        <v>24.11818589862286</v>
+        <v>33.11922935498931</v>
       </c>
       <c r="I7">
-        <v>0.0603310874123011</v>
+        <v>0.0595637449391166</v>
       </c>
       <c r="J7">
-        <v>0.02756990279218696</v>
+        <v>0.02686400088884064</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="M7">
-        <v>539.6333333333333</v>
+        <v>497.2333333333333</v>
       </c>
       <c r="N7">
-        <v>2.075905829401295</v>
+        <v>13.48220714272953</v>
       </c>
       <c r="O7">
-        <v>0.06157946513777324</v>
+        <v>0.04611994595751184</v>
       </c>
       <c r="P7">
-        <v>0.04391783681326265</v>
+        <v>0.02123519526177717</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="S7">
-        <v>32.66666666666666</v>
+        <v>257.0333333333334</v>
       </c>
       <c r="T7">
-        <v>3.197299075455286</v>
+        <v>5.616538287347484</v>
       </c>
       <c r="U7">
-        <v>0.05175137134783908</v>
+        <v>0.07146086962675158</v>
       </c>
       <c r="V7">
-        <v>0.02010931937506449</v>
+        <v>0.03155277325440886</v>
       </c>
       <c r="W7">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Y7">
-        <v>304.6</v>
+        <v>98</v>
       </c>
       <c r="Z7">
-        <v>6.716709278941336</v>
+        <v>7.691853786863721</v>
       </c>
       <c r="AA7">
-        <v>0.0626962836503836</v>
+        <v>0.06025533274599565</v>
       </c>
       <c r="AB7">
-        <v>0.02501057762621962</v>
+        <v>0.02722697280739207</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE7">
-        <v>109.5333333333333</v>
+        <v>139.2333333333333</v>
       </c>
       <c r="AF7">
-        <v>6.701908730020222</v>
+        <v>7.266513984912966</v>
       </c>
       <c r="AG7">
-        <v>0.04456474815050512</v>
+        <v>0.07559231168616794</v>
       </c>
       <c r="AH7">
-        <v>0.01476428593099074</v>
+        <v>0.03080789001817305</v>
       </c>
       <c r="AI7">
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK7">
-        <v>156.0333333333333</v>
+        <v>110.5</v>
       </c>
       <c r="AL7">
-        <v>37.25772928172731</v>
+        <v>46.144515517199</v>
       </c>
       <c r="AM7">
-        <v>0.04001395992325563</v>
+        <v>0.06148579926544673</v>
       </c>
       <c r="AN7">
-        <v>0.01240028898877643</v>
+        <v>0.02564649890821999</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>18184</v>
+        <v>18204</v>
       </c>
       <c r="AQ7">
-        <v>18085</v>
+        <v>18145</v>
       </c>
       <c r="AR7">
-        <v>606.162688</v>
+        <v>606.760845</v>
       </c>
       <c r="AS7">
-        <v>19203</v>
+        <v>781</v>
       </c>
       <c r="AT7">
         <v>0</v>
@@ -1291,136 +1291,136 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>0.2134359272042332</v>
+        <v>3.974052201516958</v>
       </c>
       <c r="C8">
-        <v>0.02786709638275353</v>
+        <v>0.04940972922072238</v>
       </c>
       <c r="D8">
-        <v>0.01993818824282684</v>
+        <v>0.01717710812520311</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G8">
-        <v>37.8</v>
+        <v>130.7666666666667</v>
       </c>
       <c r="H8">
-        <v>51.13717972004019</v>
+        <v>29.73805719514007</v>
       </c>
       <c r="I8">
-        <v>0.07516309615711873</v>
+        <v>0.05164499904575712</v>
       </c>
       <c r="J8">
-        <v>0.03232590202996696</v>
+        <v>0.02272531296523957</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M8">
-        <v>565.5</v>
+        <v>473.6666666666667</v>
       </c>
       <c r="N8">
-        <v>9.215439944256499</v>
+        <v>8.469097578939708</v>
       </c>
       <c r="O8">
-        <v>0.04515282146705381</v>
+        <v>0.05324056357197997</v>
       </c>
       <c r="P8">
-        <v>0.01251748951938246</v>
+        <v>0.02737953679180673</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S8">
-        <v>179.3</v>
+        <v>152.9333333333333</v>
       </c>
       <c r="T8">
-        <v>4.316930556451453</v>
+        <v>5.852751560932817</v>
       </c>
       <c r="U8">
-        <v>0.06696613058376563</v>
+        <v>0.05287122532448896</v>
       </c>
       <c r="V8">
-        <v>0.0431492007765296</v>
+        <v>0.02313969564546186</v>
       </c>
       <c r="W8">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8">
-        <v>66.36666666666666</v>
+        <v>119.3</v>
       </c>
       <c r="Z8">
-        <v>14.19166893797273</v>
+        <v>10.76093133666426</v>
       </c>
       <c r="AA8">
-        <v>0.06622648423529026</v>
+        <v>0.04608995110950474</v>
       </c>
       <c r="AB8">
-        <v>0.027812651919925</v>
+        <v>0.01594899156464317</v>
       </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="AE8">
-        <v>228.4333333333333</v>
+        <v>192.1</v>
       </c>
       <c r="AF8">
-        <v>6.859940311866031</v>
+        <v>7.36525315583536</v>
       </c>
       <c r="AG8">
-        <v>0.1026565411544036</v>
+        <v>0.05070945723084414</v>
       </c>
       <c r="AH8">
-        <v>0.04711455158481918</v>
+        <v>0.02381520877495607</v>
       </c>
       <c r="AI8">
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="AK8">
-        <v>129.2</v>
+        <v>140.1</v>
       </c>
       <c r="AL8">
-        <v>66.75526964139226</v>
+        <v>39.55226409999257</v>
       </c>
       <c r="AM8">
-        <v>0.06950072078304315</v>
+        <v>0.05150537333125882</v>
       </c>
       <c r="AN8">
-        <v>0.02565859746360649</v>
+        <v>0.02219467663831259</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>18167</v>
+        <v>18202</v>
       </c>
       <c r="AQ8">
-        <v>18099</v>
+        <v>18133</v>
       </c>
       <c r="AR8">
-        <v>605.595661</v>
+        <v>606.764236</v>
       </c>
       <c r="AS8">
-        <v>19205</v>
+        <v>782</v>
       </c>
       <c r="AT8">
         <v>0</v>
@@ -1440,136 +1440,136 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>9.875502278820203</v>
+        <v>12.37481999187056</v>
       </c>
       <c r="C9">
-        <v>0.05093192949098032</v>
+        <v>0.0575116098677884</v>
       </c>
       <c r="D9">
-        <v>0.0223619156299013</v>
+        <v>0.02488090618872697</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G9">
-        <v>206.0333333333333</v>
+        <v>251.9333333333333</v>
       </c>
       <c r="H9">
-        <v>25.37653618049176</v>
+        <v>20.74437327400928</v>
       </c>
       <c r="I9">
-        <v>0.0554137241809781</v>
+        <v>0.05432558228909301</v>
       </c>
       <c r="J9">
-        <v>0.02405014189109731</v>
+        <v>0.02478603363029368</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M9">
-        <v>397.2</v>
+        <v>352.1666666666667</v>
       </c>
       <c r="N9">
-        <v>9.118683179606766</v>
+        <v>9.572307141740207</v>
       </c>
       <c r="O9">
-        <v>0.05374509468409916</v>
+        <v>0.06095867408168681</v>
       </c>
       <c r="P9">
-        <v>0.01990894564409736</v>
+        <v>0.0270788552024004</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="S9">
-        <v>159.4666666666667</v>
+        <v>152.6333333333333</v>
       </c>
       <c r="T9">
-        <v>4.681750147386663</v>
+        <v>9.216475178307451</v>
       </c>
       <c r="U9">
-        <v>0.06241015450415138</v>
+        <v>0.06344766500965274</v>
       </c>
       <c r="V9">
-        <v>0.03550471933859087</v>
+        <v>0.02936316994816031</v>
       </c>
       <c r="W9">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Y9">
-        <v>95</v>
+        <v>148.6333333333333</v>
       </c>
       <c r="Z9">
-        <v>8.617800003716074</v>
+        <v>9.106380318791333</v>
       </c>
       <c r="AA9">
-        <v>0.04595563996545259</v>
+        <v>0.04433161635496893</v>
       </c>
       <c r="AB9">
-        <v>0.01723821460504862</v>
+        <v>0.01981143438921132</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AE9">
-        <v>177.1333333333333</v>
+        <v>189.5333333333333</v>
       </c>
       <c r="AF9">
-        <v>10.19175550870635</v>
+        <v>4.583294736487254</v>
       </c>
       <c r="AG9">
-        <v>0.0556596447647727</v>
+        <v>0.05747460286497262</v>
       </c>
       <c r="AH9">
-        <v>0.02149110680241062</v>
+        <v>0.02983504299407616</v>
       </c>
       <c r="AI9">
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AK9">
-        <v>171.6333333333333</v>
+        <v>113.3</v>
       </c>
       <c r="AL9">
-        <v>40.12689377405692</v>
+        <v>40.67879673701981</v>
       </c>
       <c r="AM9">
-        <v>0.05505540391091898</v>
+        <v>0.05827817852114819</v>
       </c>
       <c r="AN9">
-        <v>0.02135989808545413</v>
+        <v>0.02496206566563289</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>18166</v>
+        <v>18184</v>
       </c>
       <c r="AQ9">
-        <v>18097</v>
+        <v>18123</v>
       </c>
       <c r="AR9">
-        <v>605.56576</v>
+        <v>606.163405</v>
       </c>
       <c r="AS9">
-        <v>721</v>
+        <v>845</v>
       </c>
       <c r="AT9">
         <v>0</v>
@@ -1589,136 +1589,136 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>1.051488835341776</v>
+        <v>2.245126600157269</v>
       </c>
       <c r="C10">
-        <v>0.08120402505363641</v>
+        <v>0.05055885665902751</v>
       </c>
       <c r="D10">
-        <v>0.03040755225663377</v>
+        <v>0.02682306868284714</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10">
-        <v>113.5</v>
+        <v>112.9</v>
       </c>
       <c r="H10">
-        <v>34.28682801723393</v>
+        <v>36.1086938615862</v>
       </c>
       <c r="I10">
-        <v>0.05787761457635707</v>
+        <v>0.0619162711069482</v>
       </c>
       <c r="J10">
-        <v>0.0301283870180317</v>
+        <v>0.02952635384976245</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M10">
-        <v>491.7</v>
+        <v>491.1333333333333</v>
       </c>
       <c r="N10">
-        <v>9.494085733037787</v>
+        <v>11.77974254880501</v>
       </c>
       <c r="O10">
-        <v>0.05970026963198822</v>
+        <v>0.06184416745373326</v>
       </c>
       <c r="P10">
-        <v>0.02947197593382036</v>
+        <v>0.03556609227342675</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
+        <v>32</v>
+      </c>
+      <c r="S10">
+        <v>187.9333333333333</v>
+      </c>
+      <c r="T10">
+        <v>7.872216921593308</v>
+      </c>
+      <c r="U10">
+        <v>0.05739973245699214</v>
+      </c>
+      <c r="V10">
+        <v>0.02848637618412477</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>19</v>
+      </c>
+      <c r="Y10">
+        <v>114.6333333333333</v>
+      </c>
+      <c r="Z10">
+        <v>11.18009975546205</v>
+      </c>
+      <c r="AA10">
+        <v>0.05808355179270658</v>
+      </c>
+      <c r="AB10">
+        <v>0.03213174742078102</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
         <v>35</v>
       </c>
-      <c r="S10">
-        <v>162.6333333333333</v>
-      </c>
-      <c r="T10">
-        <v>5.232727354517363</v>
-      </c>
-      <c r="U10">
-        <v>0.05765211817464637</v>
-      </c>
-      <c r="V10">
-        <v>0.02785293280469297</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>28</v>
-      </c>
-      <c r="Y10">
-        <v>100.1666666666667</v>
-      </c>
-      <c r="Z10">
-        <v>9.223893307952153</v>
-      </c>
-      <c r="AA10">
-        <v>0.0613801548201741</v>
-      </c>
-      <c r="AB10">
-        <v>0.03447396350125034</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>36</v>
-      </c>
       <c r="AE10">
-        <v>181.3</v>
+        <v>177.7333333333333</v>
       </c>
       <c r="AF10">
-        <v>9.918792933783045</v>
+        <v>8.091833708362387</v>
       </c>
       <c r="AG10">
-        <v>0.06043707452684763</v>
+        <v>0.06079395563373274</v>
       </c>
       <c r="AH10">
-        <v>0.02898394267131713</v>
+        <v>0.02895229094345479</v>
       </c>
       <c r="AI10">
         <v>0</v>
       </c>
       <c r="AJ10">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AK10">
-        <v>161.0666666666667</v>
+        <v>123.7333333333333</v>
       </c>
       <c r="AL10">
-        <v>53.8401808283724</v>
+        <v>46.83110129670173</v>
       </c>
       <c r="AM10">
-        <v>0.06788835225418427</v>
+        <v>0.0645190299761067</v>
       </c>
       <c r="AN10">
-        <v>0.02888608338830567</v>
+        <v>0.02558586658765141</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>18210</v>
+        <v>18241</v>
       </c>
       <c r="AQ10">
-        <v>18156</v>
+        <v>18121</v>
       </c>
       <c r="AR10">
-        <v>607.03296</v>
+        <v>608.0664829999999</v>
       </c>
       <c r="AS10">
-        <v>722</v>
+        <v>846</v>
       </c>
       <c r="AT10">
         <v>0</v>
@@ -1738,67 +1738,67 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>4.488921186493617</v>
+        <v>8.710420643553601</v>
       </c>
       <c r="C11">
-        <v>0.04668945803348441</v>
+        <v>0.04419220809798411</v>
       </c>
       <c r="D11">
-        <v>0.01658980437795687</v>
+        <v>0.01878471765064918</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G11">
-        <v>108.3</v>
+        <v>203.9333333333333</v>
       </c>
       <c r="H11">
-        <v>32.22750960168654</v>
+        <v>24.14251275866264</v>
       </c>
       <c r="I11">
-        <v>0.05993596292591716</v>
+        <v>0.05382021873408293</v>
       </c>
       <c r="J11">
-        <v>0.02320323094936167</v>
+        <v>0.02270293864442511</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M11">
-        <v>494.2</v>
+        <v>406.8</v>
       </c>
       <c r="N11">
-        <v>9.858984869901093</v>
+        <v>10.09125851633485</v>
       </c>
       <c r="O11">
-        <v>0.05946314217704745</v>
+        <v>0.05480378001158475</v>
       </c>
       <c r="P11">
-        <v>0.03183694115043471</v>
+        <v>0.02243302989829712</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S11">
-        <v>158.9</v>
+        <v>196.9</v>
       </c>
       <c r="T11">
-        <v>6.419446782493288</v>
+        <v>8.955038719764765</v>
       </c>
       <c r="U11">
-        <v>0.06418661552096942</v>
+        <v>0.04740624013795282</v>
       </c>
       <c r="V11">
-        <v>0.01911850613445412</v>
+        <v>0.02020393082072388</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -1807,67 +1807,67 @@
         <v>21</v>
       </c>
       <c r="Y11">
-        <v>114.9666666666667</v>
+        <v>168.4333333333333</v>
       </c>
       <c r="Z11">
-        <v>8.192121142210176</v>
+        <v>6.82819306146647</v>
       </c>
       <c r="AA11">
-        <v>0.04686834777744357</v>
+        <v>0.04880548567679678</v>
       </c>
       <c r="AB11">
-        <v>0.01641464738671553</v>
+        <v>0.01581719925780208</v>
       </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>175.1666666666667</v>
+        <v>141.2333333333333</v>
       </c>
       <c r="AF11">
-        <v>7.965998223303085</v>
+        <v>5.190728391518116</v>
       </c>
       <c r="AG11">
-        <v>0.0652932006549358</v>
+        <v>0.05322443352788107</v>
       </c>
       <c r="AH11">
-        <v>0.02461057437729161</v>
+        <v>0.02200350749779038</v>
       </c>
       <c r="AI11">
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AK11">
-        <v>153.4666666666667</v>
+        <v>104.1666666666667</v>
       </c>
       <c r="AL11">
-        <v>41.40039739795708</v>
+        <v>37.78660279205024</v>
       </c>
       <c r="AM11">
-        <v>0.05731546322738235</v>
+        <v>0.05245165038974398</v>
       </c>
       <c r="AN11">
-        <v>0.02196282041071163</v>
+        <v>0.01951691497685626</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>18165</v>
+        <v>18384</v>
       </c>
       <c r="AQ11">
-        <v>18075</v>
+        <v>18322</v>
       </c>
       <c r="AR11">
-        <v>605.530919</v>
+        <v>612.833831</v>
       </c>
       <c r="AS11">
-        <v>723</v>
+        <v>847</v>
       </c>
       <c r="AT11">
         <v>0</v>
@@ -1887,136 +1887,136 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>3.468209277193692</v>
+        <v>1.707134759556422</v>
       </c>
       <c r="C12">
-        <v>0.05604545873118204</v>
+        <v>0.04935278296358848</v>
       </c>
       <c r="D12">
-        <v>0.06113317521339676</v>
+        <v>0.03897646586042096</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G12">
-        <v>112.2333333333333</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H12">
-        <v>32.64135403044934</v>
+        <v>30.25035752983577</v>
       </c>
       <c r="I12">
-        <v>0.05773592794722165</v>
+        <v>0.0419835291138953</v>
       </c>
       <c r="J12">
-        <v>0.02486984704440564</v>
+        <v>0.0163907518527011</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="M12">
-        <v>492.6</v>
+        <v>530.5333333333333</v>
       </c>
       <c r="N12">
-        <v>12.74515124116941</v>
+        <v>5.250015793229425</v>
       </c>
       <c r="O12">
-        <v>0.0463625593522308</v>
+        <v>0.05180045163804286</v>
       </c>
       <c r="P12">
-        <v>0.02163362351194316</v>
+        <v>0.02386737882960552</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="S12">
-        <v>242.0666666666667</v>
+        <v>90.8</v>
       </c>
       <c r="T12">
-        <v>5.028711245796588</v>
+        <v>9.505708376667766</v>
       </c>
       <c r="U12">
-        <v>0.06627045917345332</v>
+        <v>0.0417509778640555</v>
       </c>
       <c r="V12">
-        <v>0.02885535225723191</v>
+        <v>0.01943305852900154</v>
       </c>
       <c r="W12">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y12">
-        <v>92.5</v>
+        <v>167.9</v>
       </c>
       <c r="Z12">
-        <v>7.530579103822258</v>
+        <v>9.227910424671782</v>
       </c>
       <c r="AA12">
-        <v>0.05813642200521909</v>
+        <v>0.03144447176506278</v>
       </c>
       <c r="AB12">
-        <v>0.02618548515521526</v>
+        <v>0.009366574422532732</v>
       </c>
       <c r="AC12">
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AE12">
-        <v>145.9666666666667</v>
+        <v>230.2333333333333</v>
       </c>
       <c r="AF12">
-        <v>8.055861386649251</v>
+        <v>6.658589545756795</v>
       </c>
       <c r="AG12">
-        <v>0.07559145144211649</v>
+        <v>0.0537448364801261</v>
       </c>
       <c r="AH12">
-        <v>0.03613266484500496</v>
+        <v>0.01993243341505112</v>
       </c>
       <c r="AI12">
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AK12">
-        <v>124.2333333333333</v>
+        <v>115.4333333333333</v>
       </c>
       <c r="AL12">
-        <v>46.144515517199</v>
+        <v>40.68086661693295</v>
       </c>
       <c r="AM12">
-        <v>0.06148579926544673</v>
+        <v>0.03841498564660895</v>
       </c>
       <c r="AN12">
-        <v>0.02564649890821999</v>
+        <v>0.01645345222167316</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>18204</v>
+        <v>18303</v>
       </c>
       <c r="AQ12">
-        <v>18145</v>
+        <v>18139</v>
       </c>
       <c r="AR12">
-        <v>606.760845</v>
+        <v>610.0609920000001</v>
       </c>
       <c r="AS12">
-        <v>781</v>
+        <v>19103</v>
       </c>
       <c r="AT12">
         <v>0</v>
@@ -2036,136 +2036,136 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>4.801678446873212</v>
+        <v>9.597748852006722</v>
       </c>
       <c r="C13">
-        <v>0.04787250263347878</v>
+        <v>0.04407803797607986</v>
       </c>
       <c r="D13">
-        <v>0.02368561840082424</v>
+        <v>0.02114837066009199</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G13">
-        <v>139.6333333333333</v>
+        <v>211.9333333333333</v>
       </c>
       <c r="H13">
-        <v>28.6860123206822</v>
+        <v>22.92794482337949</v>
       </c>
       <c r="I13">
-        <v>0.05156553539661686</v>
+        <v>0.04190723129429379</v>
       </c>
       <c r="J13">
-        <v>0.02163172661342857</v>
+        <v>0.0189285437760828</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M13">
-        <v>464.8</v>
+        <v>392.6333333333333</v>
       </c>
       <c r="N13">
-        <v>7.208046223640938</v>
+        <v>9.582394529305422</v>
       </c>
       <c r="O13">
-        <v>0.05473768723131499</v>
+        <v>0.04115689032455215</v>
       </c>
       <c r="P13">
-        <v>0.02770444023717508</v>
+        <v>0.01668812323949644</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S13">
-        <v>140.3</v>
+        <v>193.1</v>
       </c>
       <c r="T13">
-        <v>6.380293641798654</v>
+        <v>4.191441199547485</v>
       </c>
       <c r="U13">
-        <v>0.05508287524339634</v>
+        <v>0.0478819570705102</v>
       </c>
       <c r="V13">
-        <v>0.01992171556764429</v>
+        <v>0.02594885039901443</v>
       </c>
       <c r="W13">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y13">
-        <v>117.4666666666667</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z13">
-        <v>10.19087910404382</v>
+        <v>7.066416143570815</v>
       </c>
       <c r="AA13">
-        <v>0.04522055225695008</v>
+        <v>0.04191525216941486</v>
       </c>
       <c r="AB13">
-        <v>0.01602791032393466</v>
+        <v>0.01607885463376733</v>
       </c>
       <c r="AC13">
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE13">
-        <v>194.5333333333333</v>
+        <v>168.4333333333333</v>
       </c>
       <c r="AF13">
-        <v>8.161864434430669</v>
+        <v>7.66024228682528</v>
       </c>
       <c r="AG13">
-        <v>0.0503223918517941</v>
+        <v>0.04300855495118683</v>
       </c>
       <c r="AH13">
-        <v>0.02209694168011992</v>
+        <v>0.01610445777953145</v>
       </c>
       <c r="AI13">
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK13">
-        <v>152.1333333333333</v>
+        <v>165.1333333333333</v>
       </c>
       <c r="AL13">
-        <v>39.55226409999257</v>
+        <v>37.11293807907974</v>
       </c>
       <c r="AM13">
-        <v>0.05150537333125882</v>
+        <v>0.04335754850974827</v>
       </c>
       <c r="AN13">
-        <v>0.02219467663831259</v>
+        <v>0.01572001518479627</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>18202</v>
+        <v>18213</v>
       </c>
       <c r="AQ13">
-        <v>18133</v>
+        <v>18137</v>
       </c>
       <c r="AR13">
-        <v>606.764236</v>
+        <v>607.0718460000001</v>
       </c>
       <c r="AS13">
-        <v>782</v>
+        <v>19105</v>
       </c>
       <c r="AT13">
         <v>0</v>
@@ -2185,49 +2185,49 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>12.34347772899194</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.05934354966277407</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0.03184584043996886</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="G14">
-        <v>243.9666666666667</v>
+        <v>15.23333333333333</v>
       </c>
       <c r="H14">
-        <v>20.2484309587841</v>
+        <v>61.80864759853834</v>
       </c>
       <c r="I14">
-        <v>0.05199570579911814</v>
+        <v>0.07713213230078955</v>
       </c>
       <c r="J14">
-        <v>0.02314399374379804</v>
+        <v>0.03148439879982025</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="M14">
-        <v>360.1333333333333</v>
+        <v>594.8333333333334</v>
       </c>
       <c r="N14">
-        <v>8.569984013457047</v>
+        <v>8.491813699495978</v>
       </c>
       <c r="O14">
-        <v>0.06152689838493243</v>
+        <v>0.0522052050832295</v>
       </c>
       <c r="P14">
-        <v>0.03239255354308553</v>
+        <v>0.01747920505065734</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2236,85 +2236,85 @@
         <v>28</v>
       </c>
       <c r="S14">
-        <v>137.9</v>
+        <v>164.4333333333333</v>
       </c>
       <c r="T14">
-        <v>8.770658421325475</v>
+        <v>14.21086387124648</v>
       </c>
       <c r="U14">
-        <v>0.06554462630130266</v>
+        <v>0.05233649747309135</v>
       </c>
       <c r="V14">
-        <v>0.02482211322585929</v>
+        <v>0.01967562887508269</v>
       </c>
       <c r="W14">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y14">
-        <v>143.4</v>
+        <v>215.2666666666667</v>
       </c>
       <c r="Z14">
-        <v>8.699958226630704</v>
+        <v>7.197269107632789</v>
       </c>
       <c r="AA14">
-        <v>0.04631466494213253</v>
+        <v>0.09169922049743293</v>
       </c>
       <c r="AB14">
-        <v>0.01806371103610428</v>
+        <v>0.04466329040010637</v>
       </c>
       <c r="AC14">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AE14">
-        <v>183.6</v>
+        <v>92.83333333333333</v>
       </c>
       <c r="AF14">
-        <v>6.643864464550917</v>
+        <v>9.044090459316287</v>
       </c>
       <c r="AG14">
-        <v>0.05135461267810006</v>
+        <v>0.07600006301591496</v>
       </c>
       <c r="AH14">
-        <v>0.03002967433838246</v>
+        <v>0.03692297243954584</v>
       </c>
       <c r="AI14">
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AK14">
-        <v>139.2</v>
+        <v>137.5333333333333</v>
       </c>
       <c r="AL14">
-        <v>40.67879673701981</v>
+        <v>69.06773645345442</v>
       </c>
       <c r="AM14">
-        <v>0.05827817852114819</v>
+        <v>0.07918891738173295</v>
       </c>
       <c r="AN14">
-        <v>0.02496206566563289</v>
+        <v>0.03182606546806323</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>18184</v>
+        <v>18439</v>
       </c>
       <c r="AQ14">
-        <v>18123</v>
+        <v>18302</v>
       </c>
       <c r="AR14">
-        <v>606.163405</v>
+        <v>614.663155</v>
       </c>
       <c r="AS14">
-        <v>845</v>
+        <v>19202</v>
       </c>
       <c r="AT14">
         <v>0</v>
@@ -2334,136 +2334,136 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>2.339103190959805</v>
+        <v>1.903939869817168</v>
       </c>
       <c r="C15">
-        <v>0.04941826794777435</v>
+        <v>0.03155694119176552</v>
       </c>
       <c r="D15">
-        <v>0.02608782948500186</v>
+        <v>0.009796562902647936</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G15">
-        <v>130.4666666666667</v>
+        <v>69.5</v>
       </c>
       <c r="H15">
-        <v>34.46641516757145</v>
+        <v>23.74290798409491</v>
       </c>
       <c r="I15">
-        <v>0.06194628971530412</v>
+        <v>0.06077005025654392</v>
       </c>
       <c r="J15">
-        <v>0.03121388977877278</v>
+        <v>0.02853612692908488</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="M15">
-        <v>473.5666666666667</v>
+        <v>533.3333333333334</v>
       </c>
       <c r="N15">
-        <v>10.93433260414621</v>
+        <v>2.708236534915969</v>
       </c>
       <c r="O15">
-        <v>0.06250356595274668</v>
+        <v>0.07312514855073052</v>
       </c>
       <c r="P15">
-        <v>0.0319255870422901</v>
+        <v>0.04941070535934152</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>172.7</v>
+        <v>35.76666666666667</v>
       </c>
       <c r="T15">
-        <v>7.971631223324397</v>
+        <v>3.312270326650232</v>
       </c>
       <c r="U15">
-        <v>0.05697616166013886</v>
+        <v>0.0539856264484052</v>
       </c>
       <c r="V15">
-        <v>0.02932457025970982</v>
+        <v>0.01924592287326454</v>
       </c>
       <c r="W15">
         <v>0</v>
       </c>
       <c r="X15">
+        <v>17</v>
+      </c>
+      <c r="Y15">
+        <v>309.7</v>
+      </c>
+      <c r="Z15">
+        <v>6.783085566082287</v>
+      </c>
+      <c r="AA15">
+        <v>0.05931560330543968</v>
+      </c>
+      <c r="AB15">
+        <v>0.02937328409045037</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
         <v>19</v>
       </c>
-      <c r="Y15">
-        <v>117.8</v>
-      </c>
-      <c r="Z15">
-        <v>11.57805451977752</v>
-      </c>
-      <c r="AA15">
-        <v>0.05959211768313673</v>
-      </c>
-      <c r="AB15">
-        <v>0.02942346718585913</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>29</v>
-      </c>
       <c r="AE15">
-        <v>181.2333333333333</v>
+        <v>111.9666666666667</v>
       </c>
       <c r="AF15">
-        <v>8.834240220243551</v>
+        <v>6.365152511103945</v>
       </c>
       <c r="AG15">
-        <v>0.05700509560269131</v>
+        <v>0.0447199772531694</v>
       </c>
       <c r="AH15">
-        <v>0.03031892593390225</v>
+        <v>0.01843052972769688</v>
       </c>
       <c r="AI15">
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK15">
-        <v>132.3</v>
+        <v>145.4</v>
       </c>
       <c r="AL15">
-        <v>46.83110129670173</v>
+        <v>37.25772928172731</v>
       </c>
       <c r="AM15">
-        <v>0.0645190299761067</v>
+        <v>0.04001395992325563</v>
       </c>
       <c r="AN15">
-        <v>0.02558586658765141</v>
+        <v>0.01240028898877643</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>18241</v>
+        <v>18184</v>
       </c>
       <c r="AQ15">
-        <v>18121</v>
+        <v>18085</v>
       </c>
       <c r="AR15">
-        <v>608.0664829999999</v>
+        <v>606.162688</v>
       </c>
       <c r="AS15">
-        <v>846</v>
+        <v>19203</v>
       </c>
       <c r="AT15">
         <v>0</v>
@@ -2483,136 +2483,136 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>9.151137779317187</v>
+        <v>0.2406456028369262</v>
       </c>
       <c r="C16">
-        <v>0.04444759390180041</v>
+        <v>0.04014837246275882</v>
       </c>
       <c r="D16">
-        <v>0.01708730028977252</v>
+        <v>0.01620409166449116</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
+        <v>48</v>
+      </c>
+      <c r="G16">
+        <v>39.63333333333333</v>
+      </c>
+      <c r="H16">
+        <v>49.94220326936008</v>
+      </c>
+      <c r="I16">
+        <v>0.07273667275676343</v>
+      </c>
+      <c r="J16">
+        <v>0.03056531083581672</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>50</v>
+      </c>
+      <c r="M16">
+        <v>563.6666666666666</v>
+      </c>
+      <c r="N16">
+        <v>9.623551382822118</v>
+      </c>
+      <c r="O16">
+        <v>0.04498574842660847</v>
+      </c>
+      <c r="P16">
+        <v>0.01865778838243282</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>38</v>
+      </c>
+      <c r="S16">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="T16">
+        <v>3.528566580463916</v>
+      </c>
+      <c r="U16">
+        <v>0.06137527737890885</v>
+      </c>
+      <c r="V16">
+        <v>0.03153899081685775</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>23</v>
+      </c>
+      <c r="Y16">
+        <v>66.46666666666667</v>
+      </c>
+      <c r="Z16">
+        <v>13.94980765681956</v>
+      </c>
+      <c r="AA16">
+        <v>0.06402905755165333</v>
+      </c>
+      <c r="AB16">
+        <v>0.02897027102881853</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>60</v>
+      </c>
+      <c r="AE16">
+        <v>227.1666666666667</v>
+      </c>
+      <c r="AF16">
+        <v>5.823011023793594</v>
+      </c>
+      <c r="AG16">
+        <v>0.09428380547971035</v>
+      </c>
+      <c r="AH16">
+        <v>0.04986371834357786</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
         <v>45</v>
       </c>
-      <c r="G16">
-        <v>212.9666666666667</v>
-      </c>
-      <c r="H16">
-        <v>24.49984938499313</v>
-      </c>
-      <c r="I16">
-        <v>0.05456251729470239</v>
-      </c>
-      <c r="J16">
-        <v>0.02156851605503213</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>44</v>
-      </c>
-      <c r="M16">
-        <v>397.7666666666667</v>
-      </c>
-      <c r="N16">
-        <v>9.498000302186732</v>
-      </c>
-      <c r="O16">
-        <v>0.05347150147384293</v>
-      </c>
-      <c r="P16">
-        <v>0.02208301661533521</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>27</v>
-      </c>
-      <c r="S16">
-        <v>181.3666666666667</v>
-      </c>
-      <c r="T16">
-        <v>9.403187526033541</v>
-      </c>
-      <c r="U16">
-        <v>0.05020330363715596</v>
-      </c>
-      <c r="V16">
-        <v>0.01899294597272164</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>20</v>
-      </c>
-      <c r="Y16">
-        <v>170.8</v>
-      </c>
-      <c r="Z16">
-        <v>7.00995451639964</v>
-      </c>
-      <c r="AA16">
-        <v>0.04974830645105175</v>
-      </c>
-      <c r="AB16">
-        <v>0.0198680338012033</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>21</v>
-      </c>
-      <c r="AE16">
-        <v>148.0666666666667</v>
-      </c>
-      <c r="AF16">
-        <v>5.580951266689842</v>
-      </c>
-      <c r="AG16">
-        <v>0.05333754702513686</v>
-      </c>
-      <c r="AH16">
-        <v>0.02039261435523012</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>16</v>
-      </c>
       <c r="AK16">
-        <v>110.5</v>
+        <v>124.3333333333333</v>
       </c>
       <c r="AL16">
-        <v>37.78660279205024</v>
+        <v>66.75526964139226</v>
       </c>
       <c r="AM16">
-        <v>0.05245165038974398</v>
+        <v>0.06950072078304315</v>
       </c>
       <c r="AN16">
-        <v>0.01951691497685626</v>
+        <v>0.02565859746360649</v>
       </c>
       <c r="AO16">
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>18384</v>
+        <v>18167</v>
       </c>
       <c r="AQ16">
-        <v>18322</v>
+        <v>18099</v>
       </c>
       <c r="AR16">
-        <v>612.833831</v>
+        <v>605.595661</v>
       </c>
       <c r="AS16">
-        <v>847</v>
+        <v>19205</v>
       </c>
       <c r="AT16">
         <v>0</v>
